--- a/outputs/54675.xlsx
+++ b/outputs/54675.xlsx
@@ -710,8 +710,8 @@
         <v>3</v>
       </c>
       <c r="F3" s="8" t="n">
-        <f aca="false">COUNTIFS(B:B,"*Gary Stoddard*",A:A,"4")</f>
-        <v>14</v>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("Gary Stoddard",B2:B120)),--(A2:A120=4))</f>
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
